--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_5.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02018323374344335</v>
+        <v>0.01445569023219714</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008434905534077259</v>
+        <v>0.008428503609948769</v>
       </c>
       <c r="C2" t="n">
-        <v>31481385</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31481385</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>22318906</v>
+        <v>4328909</v>
       </c>
       <c r="L2" t="n">
-        <v>12801542</v>
+        <v>2355386</v>
       </c>
       <c r="M2" t="n">
-        <v>3140987</v>
+        <v>534164</v>
       </c>
       <c r="N2" t="n">
-        <v>149280</v>
+        <v>18895</v>
       </c>
       <c r="O2" t="n">
-        <v>1939298</v>
+        <v>350263</v>
       </c>
       <c r="P2" t="n">
-        <v>763069</v>
+        <v>127718</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999945163726807</v>
+        <v>0.9999933242797852</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8892579674720764</v>
+        <v>0.851405143737793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7688765525817871</v>
+        <v>0.7041053771972656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7123039960861206</v>
+        <v>0.6361246109008789</v>
       </c>
       <c r="U2" t="n">
-        <v>0.461056649684906</v>
+        <v>0.2667466700077057</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7577167749404907</v>
+        <v>0.6777744889259338</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8388774991035461</v>
+        <v>0.8002481460571289</v>
       </c>
       <c r="X2" t="n">
-        <v>31481385</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31481385</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>23990435</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14816851</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3994341</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294653</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295121</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565010666847229</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112791419029236</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582428097724915</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623663306236267</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020397067070007</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004939335007177735</v>
+        <v>0.00345289751345278</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002023222468713518</v>
+        <v>0.002021233558325551</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>22318906</v>
+        <v>4328909</v>
       </c>
       <c r="E3" t="n">
-        <v>2679610</v>
+        <v>676954</v>
       </c>
       <c r="F3" t="n">
-        <v>47295</v>
+        <v>10144</v>
       </c>
       <c r="G3" t="n">
-        <v>4681</v>
+        <v>722</v>
       </c>
       <c r="H3" t="n">
-        <v>3170</v>
+        <v>812</v>
       </c>
       <c r="I3" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>49950442</v>
+        <v>10016580</v>
       </c>
       <c r="K3" t="n">
-        <v>53598784</v>
+        <v>10556507</v>
       </c>
       <c r="L3" t="n">
-        <v>61301849</v>
+        <v>12066341</v>
       </c>
       <c r="M3" t="n">
-        <v>75505826</v>
+        <v>15090629</v>
       </c>
       <c r="N3" t="n">
-        <v>80812303</v>
+        <v>16188402</v>
       </c>
       <c r="O3" t="n">
-        <v>78266410</v>
+        <v>15653527</v>
       </c>
       <c r="P3" t="n">
-        <v>80318853</v>
+        <v>16104327</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8908400535583496</v>
+        <v>0.8627495765686035</v>
       </c>
       <c r="S3" t="n">
-        <v>0.786237895488739</v>
+        <v>0.71954745054245</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6743867993354797</v>
+        <v>0.5722660422325134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3353107273578644</v>
+        <v>0.2116897106170654</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7618561387062073</v>
+        <v>0.6873940229415894</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7894484400749207</v>
+        <v>0.6604065299034119</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>23990435</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>986642</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42469</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33887</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>49950615</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55287209</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63707431</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76114704</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>80836605</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78637262</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80399145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957557737827301</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100130200386047</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576065301895142</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618456244468689</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016417860984802</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05374180970213394</v>
+        <v>0.04176483442163876</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03191956356972928</v>
+        <v>0.03189864197131144</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2625189</v>
+        <v>713172</v>
       </c>
       <c r="E4" t="n">
-        <v>12801542</v>
+        <v>2355386</v>
       </c>
       <c r="F4" t="n">
-        <v>761670</v>
+        <v>178534</v>
       </c>
       <c r="G4" t="n">
-        <v>23865</v>
+        <v>7229</v>
       </c>
       <c r="H4" t="n">
-        <v>65045</v>
+        <v>17965</v>
       </c>
       <c r="I4" t="n">
-        <v>4710</v>
+        <v>1141</v>
       </c>
       <c r="J4" t="n">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>2779442</v>
+        <v>755520</v>
       </c>
       <c r="L4" t="n">
-        <v>3848130</v>
+        <v>989832</v>
       </c>
       <c r="M4" t="n">
-        <v>1268629</v>
+        <v>305552</v>
       </c>
       <c r="N4" t="n">
-        <v>174498</v>
+        <v>51940</v>
       </c>
       <c r="O4" t="n">
-        <v>620099</v>
+        <v>166521</v>
       </c>
       <c r="P4" t="n">
-        <v>146562</v>
+        <v>31880</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999972581863403</v>
+        <v>0.9999966621398926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8900483250617981</v>
+        <v>0.8570398092269897</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7774603366851807</v>
+        <v>0.711742639541626</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6928269863128662</v>
+        <v>0.6025079488754272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3882560729980469</v>
+        <v>0.2360503077507019</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7597807645797729</v>
+        <v>0.682550311088562</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8134127259254456</v>
+        <v>0.7236331701278687</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1018542</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14816851</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>413179</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27399</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5710</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1091017</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1442548</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>659751</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150196</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249247</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570291042327881</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106456637382507</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579245209693909</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6621058583259583</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018406867980957</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>98038</v>
+        <v>27700</v>
       </c>
       <c r="E5" t="n">
-        <v>1004000</v>
+        <v>268500</v>
       </c>
       <c r="F5" t="n">
-        <v>3140987</v>
+        <v>534164</v>
       </c>
       <c r="G5" t="n">
-        <v>72880</v>
+        <v>19674</v>
       </c>
       <c r="H5" t="n">
-        <v>318393</v>
+        <v>77340</v>
       </c>
       <c r="I5" t="n">
-        <v>23229</v>
+        <v>6037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2734868</v>
+        <v>688664</v>
       </c>
       <c r="L5" t="n">
-        <v>3480479</v>
+        <v>918041</v>
       </c>
       <c r="M5" t="n">
-        <v>1516558</v>
+        <v>399255</v>
       </c>
       <c r="N5" t="n">
-        <v>295919</v>
+        <v>70363</v>
       </c>
       <c r="O5" t="n">
-        <v>606193</v>
+        <v>159289</v>
       </c>
       <c r="P5" t="n">
-        <v>203516</v>
+        <v>65675</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999978542327881</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9322832822799683</v>
+        <v>0.9115603566169739</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9100033044815063</v>
+        <v>0.8831647634506226</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9657973647117615</v>
+        <v>0.9568386673927307</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942231774330139</v>
+        <v>0.9925103783607483</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9849408864974976</v>
+        <v>0.980047881603241</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957009553909302</v>
+        <v>0.9940258860588074</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>39993</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>424764</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3994341</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49694</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145588</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1063339</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1465170</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663204</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150546</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250370</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735441207885742</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642927050590515</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837538599967957</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996306836605072</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938645958900452</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983707666397095</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>54427</v>
+        <v>14260</v>
       </c>
       <c r="E6" t="n">
-        <v>86494</v>
+        <v>20272</v>
       </c>
       <c r="F6" t="n">
-        <v>97077</v>
+        <v>23197</v>
       </c>
       <c r="G6" t="n">
-        <v>149280</v>
+        <v>18895</v>
       </c>
       <c r="H6" t="n">
-        <v>53286</v>
+        <v>11653</v>
       </c>
       <c r="I6" t="n">
-        <v>4585</v>
+        <v>966</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32203</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26690</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54367</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294653</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34881</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1644</v>
+        <v>346</v>
       </c>
       <c r="E7" t="n">
-        <v>73774</v>
+        <v>22964</v>
       </c>
       <c r="F7" t="n">
-        <v>348241</v>
+        <v>89456</v>
       </c>
       <c r="G7" t="n">
-        <v>68546</v>
+        <v>22811</v>
       </c>
       <c r="H7" t="n">
-        <v>1939298</v>
+        <v>350263</v>
       </c>
       <c r="I7" t="n">
-        <v>113947</v>
+        <v>23712</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4047</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148085</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37889</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295121</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>4252</v>
+        <v>1142</v>
       </c>
       <c r="F8" t="n">
-        <v>14346</v>
+        <v>4221</v>
       </c>
       <c r="G8" t="n">
-        <v>4526</v>
+        <v>1504</v>
       </c>
       <c r="H8" t="n">
-        <v>180205</v>
+        <v>58751</v>
       </c>
       <c r="I8" t="n">
-        <v>763069</v>
+        <v>127718</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
